--- a/razao_de_suporte/razao_suporte_rj.xlsx
+++ b/razao_de_suporte/razao_suporte_rj.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28227"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gisel\PycharmProjects\Tcc_demografia\razao_de_suporte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{D842A309-7023-4AE1-8CA2-ACA393091560}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968BEE67-0AA5-45ED-9EAF-FB32F0278D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="38640" windowHeight="21120" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="4" uniqueCount="4">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="7" uniqueCount="5">
   <si>
     <t>Ano</t>
   </si>
@@ -46,12 +46,18 @@
   <si>
     <t>-</t>
   </si>
+  <si>
+    <t>PIB per capita (R$ Mil - constantes de 2010)</t>
+  </si>
 </sst>
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="5" x14ac:knownFonts="1">
+  <numFmts count="1">
+    <numFmt numFmtId="165" formatCode="#,##0.000"/>
+  </numFmts>
+  <fonts count="6" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -85,6 +91,14 @@
       <name val="Aptos Narrow"/>
       <family val="2"/>
     </font>
+    <font>
+      <b/>
+      <sz val="11"/>
+      <color theme="1"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -94,7 +108,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="10">
+  <borders count="13">
     <border>
       <left/>
       <right/>
@@ -229,6 +243,45 @@
       <right style="thin">
         <color auto="1"/>
       </right>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="medium">
+        <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="medium">
+        <color indexed="64"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
+      <top style="thin">
+        <color auto="1"/>
+      </top>
+      <bottom style="thin">
+        <color auto="1"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right/>
       <top style="thin">
         <color auto="1"/>
       </top>
@@ -242,7 +295,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="10">
+  <cellXfs count="18">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -266,6 +319,28 @@
     </xf>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="5" fillId="0" borderId="10" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="10" fontId="0" fillId="0" borderId="3" xfId="1" applyNumberFormat="1" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="8" xfId="0" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -570,12 +645,12 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:E8"/>
+  <dimension ref="C1:E18"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
     <col min="2" max="2" width="22.140625" customWidth="1"/>
-    <col min="4" max="4" width="17.42578125" bestFit="1" customWidth="1"/>
+    <col min="4" max="4" width="21.42578125" customWidth="1"/>
     <col min="5" max="5" width="36.85546875" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
@@ -662,6 +737,87 @@
         <v>3</v>
       </c>
     </row>
+    <row r="11" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="12" spans="3:5" ht="45" x14ac:dyDescent="0.25">
+      <c r="C12" s="10" t="s">
+        <v>0</v>
+      </c>
+      <c r="D12" s="11" t="s">
+        <v>4</v>
+      </c>
+      <c r="E12" s="1" t="s">
+        <v>2</v>
+      </c>
+    </row>
+    <row r="13" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C13" s="12">
+        <v>2010</v>
+      </c>
+      <c r="D13" s="16">
+        <v>28.134</v>
+      </c>
+      <c r="E13" s="13">
+        <f xml:space="preserve"> (D13 / D14)^(1 / 10) - 1</f>
+        <v>2.7033162791539667E-2</v>
+      </c>
+    </row>
+    <row r="14" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C14" s="12">
+        <v>2000</v>
+      </c>
+      <c r="D14" s="16">
+        <v>21.547000000000001</v>
+      </c>
+      <c r="E14" s="13">
+        <f xml:space="preserve"> (D14 / D15)^(1 / 10) - 1</f>
+        <v>-1.5233355422892281E-3</v>
+      </c>
+    </row>
+    <row r="15" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C15" s="12">
+        <v>1991</v>
+      </c>
+      <c r="D15" s="16">
+        <v>21.878</v>
+      </c>
+      <c r="E15" s="13">
+        <f xml:space="preserve"> (D15 / D16)^(1 / 10) - 1</f>
+        <v>-4.0888085242101191E-3</v>
+      </c>
+    </row>
+    <row r="16" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C16" s="12">
+        <v>1980</v>
+      </c>
+      <c r="D16" s="16">
+        <v>22.792999999999999</v>
+      </c>
+      <c r="E16" s="13">
+        <f xml:space="preserve"> (D16 / D17)^(1 / 10) - 1</f>
+        <v>4.1292975471554527E-2</v>
+      </c>
+    </row>
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="12">
+        <v>1970</v>
+      </c>
+      <c r="D17" s="16">
+        <v>15.208</v>
+      </c>
+      <c r="E17" s="13">
+        <f xml:space="preserve"> (D17 / D18)^(1 / 10) - 1</f>
+        <v>2.7442834573832675E-2</v>
+      </c>
+    </row>
+    <row r="18" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C18" s="14">
+        <v>1960</v>
+      </c>
+      <c r="D18" s="17">
+        <v>11.601000000000001</v>
+      </c>
+      <c r="E18" s="15"/>
+    </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/razao_de_suporte/razao_suporte_rj.xlsx
+++ b/razao_de_suporte/razao_suporte_rj.xlsx
@@ -1,21 +1,21 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="28623"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="7" rupBuild="29725"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
       <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\gisel\PycharmProjects\Tcc_demografia\razao_de_suporte\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{968BEE67-0AA5-45ED-9EAF-FB32F0278D5C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EFB968DC-DC25-433B-B29B-E7CDE8C7D75D}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="-28920" yWindow="-120" windowWidth="29040" windowHeight="15720" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" iterate="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -55,9 +55,9 @@
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
   <numFmts count="1">
-    <numFmt numFmtId="165" formatCode="#,##0.000"/>
+    <numFmt numFmtId="164" formatCode="#,##0.000"/>
   </numFmts>
-  <fonts count="6" x14ac:knownFonts="1">
+  <fonts count="7" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -99,6 +99,11 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <sz val="12"/>
+      <name val="Aptos Narrow"/>
+      <family val="2"/>
+    </font>
   </fonts>
   <fills count="2">
     <fill>
@@ -108,7 +113,7 @@
       <patternFill patternType="gray125"/>
     </fill>
   </fills>
-  <borders count="13">
+  <borders count="14">
     <border>
       <left/>
       <right/>
@@ -287,6 +292,19 @@
       </top>
       <bottom style="medium">
         <color indexed="64"/>
+      </bottom>
+      <diagonal/>
+    </border>
+    <border>
+      <left style="thin">
+        <color auto="1"/>
+      </left>
+      <right style="thin">
+        <color auto="1"/>
+      </right>
+      <top/>
+      <bottom style="thin">
+        <color auto="1"/>
       </bottom>
       <diagonal/>
     </border>
@@ -295,7 +313,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="19">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="2" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -306,20 +324,12 @@
     <xf numFmtId="0" fontId="3" fillId="0" borderId="4" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
     <xf numFmtId="0" fontId="4" fillId="0" borderId="6" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="top"/>
     </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1"/>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
-    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="5" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
@@ -336,11 +346,26 @@
       <alignment vertical="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="0" fillId="0" borderId="4" xfId="0" applyBorder="1"/>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="11" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="165" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="12" xfId="0" applyNumberFormat="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="8" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="6" fillId="0" borderId="13" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="top"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="3" fillId="0" borderId="9" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="2">
@@ -645,7 +670,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="C1:E18"/>
+  <dimension ref="C1:E19"/>
   <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="5" bestFit="1" customWidth="1"/>
@@ -656,10 +681,10 @@
   <sheetData>
     <row r="1" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
     <row r="2" spans="3:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C2" s="5" t="s">
+      <c r="C2" s="4" t="s">
         <v>0</v>
       </c>
-      <c r="D2" s="6" t="s">
+      <c r="D2" s="5" t="s">
         <v>1</v>
       </c>
       <c r="E2" s="1" t="s">
@@ -667,156 +692,168 @@
       </c>
     </row>
     <row r="3" spans="3:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C3" s="8">
+      <c r="C3" s="14">
+        <v>2022</v>
+      </c>
+      <c r="D3" s="16">
+        <v>2.2373629780000002</v>
+      </c>
+      <c r="E3" s="2">
+        <f t="shared" ref="E3:E7" si="0" xml:space="preserve"> (D3 / D4)^(1 / 10) - 1</f>
+        <v>-3.7000950297330082E-3</v>
+      </c>
+    </row>
+    <row r="4" spans="3:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C4" s="14">
         <v>2010</v>
       </c>
-      <c r="D3" s="4">
+      <c r="D4" s="17">
         <v>2.3218574806481129</v>
-      </c>
-      <c r="E3" s="2">
-        <f t="shared" ref="E3:E6" si="0" xml:space="preserve"> (D3 / D4)^(1 / 10) - 1</f>
-        <v>1.1655062258999926E-2</v>
-      </c>
-    </row>
-    <row r="4" spans="3:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C4" s="8">
-        <v>2000</v>
-      </c>
-      <c r="D4" s="4">
-        <v>2.067811603377617</v>
       </c>
       <c r="E4" s="2">
         <f t="shared" si="0"/>
-        <v>7.6764305825398615E-3</v>
+        <v>1.1655062258999926E-2</v>
       </c>
     </row>
     <row r="5" spans="3:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C5" s="8">
-        <v>1991</v>
-      </c>
-      <c r="D5" s="4">
-        <v>1.9155785358583259</v>
+      <c r="C5" s="14">
+        <v>2000</v>
+      </c>
+      <c r="D5" s="17">
+        <v>2.067811603377617</v>
       </c>
       <c r="E5" s="2">
         <f t="shared" si="0"/>
-        <v>7.2388306885824427E-3</v>
+        <v>7.6764305825398615E-3</v>
       </c>
     </row>
     <row r="6" spans="3:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C6" s="8">
-        <v>1980</v>
-      </c>
-      <c r="D6" s="4">
-        <v>1.782277647151707</v>
+      <c r="C6" s="14">
+        <v>1991</v>
+      </c>
+      <c r="D6" s="17">
+        <v>1.9155785358583259</v>
       </c>
       <c r="E6" s="2">
         <f t="shared" si="0"/>
+        <v>7.2388306885824427E-3</v>
+      </c>
+    </row>
+    <row r="7" spans="3:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C7" s="14">
+        <v>1980</v>
+      </c>
+      <c r="D7" s="17">
+        <v>1.782277647151707</v>
+      </c>
+      <c r="E7" s="2">
+        <f t="shared" si="0"/>
         <v>3.2101091530111869E-2</v>
       </c>
     </row>
-    <row r="7" spans="3:5" ht="15.75" x14ac:dyDescent="0.25">
-      <c r="C7" s="8">
+    <row r="8" spans="3:5" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="C8" s="14">
         <v>1970</v>
       </c>
-      <c r="D7" s="4">
+      <c r="D8" s="17">
         <v>1.2994302922529251</v>
       </c>
-      <c r="E7" s="2">
-        <f xml:space="preserve"> (D7 / D8)^(1 / 10) - 1</f>
+      <c r="E8" s="2">
+        <f xml:space="preserve"> (D8 / D9)^(1 / 10) - 1</f>
         <v>7.5541145140542998E-3</v>
       </c>
     </row>
-    <row r="8" spans="3:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C8" s="9">
+    <row r="9" spans="3:5" ht="16.5" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C9" s="15">
         <v>1960</v>
       </c>
-      <c r="D8" s="7">
+      <c r="D9" s="18">
         <v>1.2052279039372651</v>
       </c>
-      <c r="E8" s="3" t="s">
+      <c r="E9" s="3" t="s">
         <v>3</v>
       </c>
     </row>
-    <row r="11" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
-    <row r="12" spans="3:5" ht="45" x14ac:dyDescent="0.25">
-      <c r="C12" s="10" t="s">
+    <row r="12" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3"/>
+    <row r="13" spans="3:5" ht="30" x14ac:dyDescent="0.25">
+      <c r="C13" s="6" t="s">
         <v>0</v>
       </c>
-      <c r="D12" s="11" t="s">
+      <c r="D13" s="7" t="s">
         <v>4</v>
       </c>
-      <c r="E12" s="1" t="s">
+      <c r="E13" s="1" t="s">
         <v>2</v>
       </c>
     </row>
-    <row r="13" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C13" s="12">
+    <row r="14" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C14" s="8">
         <v>2010</v>
       </c>
-      <c r="D13" s="16">
+      <c r="D14" s="12">
         <v>28.134</v>
       </c>
-      <c r="E13" s="13">
-        <f xml:space="preserve"> (D13 / D14)^(1 / 10) - 1</f>
+      <c r="E14" s="9">
+        <f xml:space="preserve"> (D14 / D15)^(1 / 10) - 1</f>
         <v>2.7033162791539667E-2</v>
       </c>
     </row>
-    <row r="14" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C14" s="12">
+    <row r="15" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C15" s="8">
         <v>2000</v>
       </c>
-      <c r="D14" s="16">
+      <c r="D15" s="12">
         <v>21.547000000000001</v>
       </c>
-      <c r="E14" s="13">
-        <f xml:space="preserve"> (D14 / D15)^(1 / 10) - 1</f>
+      <c r="E15" s="9">
+        <f xml:space="preserve"> (D15 / D16)^(1 / 10) - 1</f>
         <v>-1.5233355422892281E-3</v>
       </c>
     </row>
-    <row r="15" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C15" s="12">
+    <row r="16" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C16" s="8">
         <v>1991</v>
       </c>
-      <c r="D15" s="16">
+      <c r="D16" s="12">
         <v>21.878</v>
       </c>
-      <c r="E15" s="13">
-        <f xml:space="preserve"> (D15 / D16)^(1 / 10) - 1</f>
+      <c r="E16" s="9">
+        <f xml:space="preserve"> (D16 / D17)^(1 / 10) - 1</f>
         <v>-4.0888085242101191E-3</v>
       </c>
     </row>
-    <row r="16" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C16" s="12">
+    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C17" s="8">
         <v>1980</v>
       </c>
-      <c r="D16" s="16">
+      <c r="D17" s="12">
         <v>22.792999999999999</v>
       </c>
-      <c r="E16" s="13">
-        <f xml:space="preserve"> (D16 / D17)^(1 / 10) - 1</f>
+      <c r="E17" s="9">
+        <f xml:space="preserve"> (D17 / D18)^(1 / 10) - 1</f>
         <v>4.1292975471554527E-2</v>
       </c>
     </row>
-    <row r="17" spans="3:5" x14ac:dyDescent="0.25">
-      <c r="C17" s="12">
+    <row r="18" spans="3:5" x14ac:dyDescent="0.25">
+      <c r="C18" s="8">
         <v>1970</v>
       </c>
-      <c r="D17" s="16">
+      <c r="D18" s="12">
         <v>15.208</v>
       </c>
-      <c r="E17" s="13">
-        <f xml:space="preserve"> (D17 / D18)^(1 / 10) - 1</f>
+      <c r="E18" s="9">
+        <f xml:space="preserve"> (D18 / D19)^(1 / 10) - 1</f>
         <v>2.7442834573832675E-2</v>
       </c>
     </row>
-    <row r="18" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
-      <c r="C18" s="14">
+    <row r="19" spans="3:5" ht="15.75" thickBot="1" x14ac:dyDescent="0.3">
+      <c r="C19" s="10">
         <v>1960</v>
       </c>
-      <c r="D18" s="17">
+      <c r="D19" s="13">
         <v>11.601000000000001</v>
       </c>
-      <c r="E18" s="15"/>
+      <c r="E19" s="11"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
